--- a/기초데이터/원본/인덱스.xlsx
+++ b/기초데이터/원본/인덱스.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20397"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\passive\Remodeling_SW\기초데이터\원본\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Remodeling_SW\기초데이터\원본\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2426D4EF-C4B8-4F7E-9759-80F6BCE08EFF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16800" xr2:uid="{DC5B3144-6D0B-4F19-A3D8-1A461711D133}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1014,7 +1013,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="&quot;주 &quot;0.0&quot; 일 근무&quot;"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -1203,7 +1205,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1257,6 +1259,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1571,8 +1579,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA765F3-472C-4E33-A87A-05F3E93FF046}">
-  <dimension ref="A1:F719"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F720"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.125" style="2" bestFit="1" customWidth="1"/>
@@ -11716,7 +11724,7 @@
       <c r="C594" s="2">
         <v>104</v>
       </c>
-      <c r="D594" s="2">
+      <c r="D594" s="18">
         <v>9.7144514654701197E-17</v>
       </c>
       <c r="E594" s="1">
@@ -11733,7 +11741,7 @@
       <c r="C595" s="2">
         <v>104</v>
       </c>
-      <c r="D595" s="2">
+      <c r="D595" s="18">
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="E595" s="1">
@@ -11750,7 +11758,7 @@
       <c r="C596" s="2">
         <v>104</v>
       </c>
-      <c r="D596" s="2">
+      <c r="D596" s="18">
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="E596" s="1">
@@ -11767,7 +11775,7 @@
       <c r="C597" s="2">
         <v>104</v>
       </c>
-      <c r="D597" s="2">
+      <c r="D597" s="18">
         <v>0.125</v>
       </c>
       <c r="E597" s="1">
@@ -11784,7 +11792,7 @@
       <c r="C598" s="2">
         <v>104</v>
       </c>
-      <c r="D598" s="2">
+      <c r="D598" s="18">
         <v>0.16666666666666699</v>
       </c>
       <c r="E598" s="1">
@@ -11801,7 +11809,7 @@
       <c r="C599" s="2">
         <v>104</v>
       </c>
-      <c r="D599" s="2">
+      <c r="D599" s="18">
         <v>0.20833333333333301</v>
       </c>
       <c r="E599" s="1">
@@ -11818,7 +11826,7 @@
       <c r="C600" s="2">
         <v>104</v>
       </c>
-      <c r="D600" s="2">
+      <c r="D600" s="18">
         <v>0.25</v>
       </c>
       <c r="E600" s="1">
@@ -11835,7 +11843,7 @@
       <c r="C601" s="2">
         <v>104</v>
       </c>
-      <c r="D601" s="2">
+      <c r="D601" s="18">
         <v>0.29166666666666702</v>
       </c>
       <c r="E601" s="1">
@@ -11852,7 +11860,7 @@
       <c r="C602" s="2">
         <v>104</v>
       </c>
-      <c r="D602" s="2">
+      <c r="D602" s="18">
         <v>0.33333333333333298</v>
       </c>
       <c r="E602" s="1">
@@ -11869,7 +11877,7 @@
       <c r="C603" s="2">
         <v>104</v>
       </c>
-      <c r="D603" s="2">
+      <c r="D603" s="18">
         <v>0.375</v>
       </c>
       <c r="E603" s="1">
@@ -11886,7 +11894,7 @@
       <c r="C604" s="2">
         <v>104</v>
       </c>
-      <c r="D604" s="2">
+      <c r="D604" s="18">
         <v>0.41666666666666702</v>
       </c>
       <c r="E604" s="1">
@@ -11903,7 +11911,7 @@
       <c r="C605" s="2">
         <v>104</v>
       </c>
-      <c r="D605" s="2">
+      <c r="D605" s="18">
         <v>0.45833333333333298</v>
       </c>
       <c r="E605" s="1">
@@ -11920,7 +11928,7 @@
       <c r="C606" s="2">
         <v>104</v>
       </c>
-      <c r="D606" s="2">
+      <c r="D606" s="18">
         <v>0.5</v>
       </c>
       <c r="E606" s="1">
@@ -11937,7 +11945,7 @@
       <c r="C607" s="2">
         <v>104</v>
       </c>
-      <c r="D607" s="2">
+      <c r="D607" s="18">
         <v>0.54166666666666696</v>
       </c>
       <c r="E607" s="1">
@@ -11954,7 +11962,7 @@
       <c r="C608" s="2">
         <v>104</v>
       </c>
-      <c r="D608" s="2">
+      <c r="D608" s="18">
         <v>0.58333333333333304</v>
       </c>
       <c r="E608" s="1">
@@ -11971,7 +11979,7 @@
       <c r="C609" s="2">
         <v>104</v>
       </c>
-      <c r="D609" s="2">
+      <c r="D609" s="18">
         <v>0.625</v>
       </c>
       <c r="E609" s="1">
@@ -11988,7 +11996,7 @@
       <c r="C610" s="2">
         <v>104</v>
       </c>
-      <c r="D610" s="2">
+      <c r="D610" s="18">
         <v>0.66666666666666696</v>
       </c>
       <c r="E610" s="1">
@@ -12005,7 +12013,7 @@
       <c r="C611" s="2">
         <v>104</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="18">
         <v>0.70833333333333304</v>
       </c>
       <c r="E611" s="1">
@@ -12022,7 +12030,7 @@
       <c r="C612" s="2">
         <v>104</v>
       </c>
-      <c r="D612" s="2">
+      <c r="D612" s="18">
         <v>0.75</v>
       </c>
       <c r="E612" s="1">
@@ -12039,7 +12047,7 @@
       <c r="C613" s="2">
         <v>104</v>
       </c>
-      <c r="D613" s="2">
+      <c r="D613" s="18">
         <v>0.79166666666666696</v>
       </c>
       <c r="E613" s="1">
@@ -12056,7 +12064,7 @@
       <c r="C614" s="2">
         <v>104</v>
       </c>
-      <c r="D614" s="2">
+      <c r="D614" s="18">
         <v>0.83333333333333304</v>
       </c>
       <c r="E614" s="1">
@@ -12073,7 +12081,7 @@
       <c r="C615" s="2">
         <v>104</v>
       </c>
-      <c r="D615" s="2">
+      <c r="D615" s="18">
         <v>0.875</v>
       </c>
       <c r="E615" s="1">
@@ -12090,7 +12098,7 @@
       <c r="C616" s="2">
         <v>104</v>
       </c>
-      <c r="D616" s="2">
+      <c r="D616" s="18">
         <v>0.91666666666666696</v>
       </c>
       <c r="E616" s="1">
@@ -12107,7 +12115,7 @@
       <c r="C617" s="2">
         <v>104</v>
       </c>
-      <c r="D617" s="2">
+      <c r="D617" s="18">
         <v>0.95833333333333304</v>
       </c>
       <c r="E617" s="1">
@@ -12124,7 +12132,7 @@
       <c r="C618" s="2">
         <v>104</v>
       </c>
-      <c r="D618" s="2">
+      <c r="D618" s="18">
         <v>0.999999999999999</v>
       </c>
       <c r="E618" s="1">
@@ -12141,8 +12149,8 @@
       <c r="C619" s="2">
         <v>105</v>
       </c>
-      <c r="D619" s="2">
-        <v>1</v>
+      <c r="D619" s="19">
+        <v>7</v>
       </c>
       <c r="E619" s="2">
         <v>1</v>
@@ -12158,8 +12166,8 @@
       <c r="C620" s="2">
         <v>105</v>
       </c>
-      <c r="D620" s="2">
-        <v>2</v>
+      <c r="D620" s="19">
+        <v>6</v>
       </c>
       <c r="E620" s="2">
         <v>2</v>
@@ -12175,8 +12183,8 @@
       <c r="C621" s="2">
         <v>105</v>
       </c>
-      <c r="D621" s="2">
-        <v>3</v>
+      <c r="D621" s="19">
+        <v>5.5</v>
       </c>
       <c r="E621" s="2">
         <v>3</v>
@@ -12192,8 +12200,8 @@
       <c r="C622" s="2">
         <v>105</v>
       </c>
-      <c r="D622" s="2">
-        <v>4</v>
+      <c r="D622" s="19">
+        <v>5</v>
       </c>
       <c r="E622" s="2">
         <v>4</v>
@@ -12209,8 +12217,8 @@
       <c r="C623" s="2">
         <v>105</v>
       </c>
-      <c r="D623" s="2">
-        <v>5</v>
+      <c r="D623" s="19">
+        <v>4</v>
       </c>
       <c r="E623" s="2">
         <v>5</v>
@@ -12226,8 +12234,8 @@
       <c r="C624" s="2">
         <v>105</v>
       </c>
-      <c r="D624" s="2">
-        <v>6</v>
+      <c r="D624" s="19">
+        <v>3</v>
       </c>
       <c r="E624" s="2">
         <v>6</v>
@@ -12243,8 +12251,8 @@
       <c r="C625" s="2">
         <v>105</v>
       </c>
-      <c r="D625" s="2">
-        <v>7</v>
+      <c r="D625" s="19">
+        <v>2</v>
       </c>
       <c r="E625" s="2">
         <v>7</v>
@@ -12258,13 +12266,13 @@
         <v>-1</v>
       </c>
       <c r="C626" s="2">
-        <v>106</v>
-      </c>
-      <c r="D626" s="2" t="s">
-        <v>232</v>
+        <v>105</v>
+      </c>
+      <c r="D626" s="19">
+        <v>1</v>
       </c>
       <c r="E626" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -12278,10 +12286,10 @@
         <v>106</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E627" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -12295,10 +12303,10 @@
         <v>106</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E628" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -12309,13 +12317,13 @@
         <v>-1</v>
       </c>
       <c r="C629" s="2">
-        <v>107</v>
-      </c>
-      <c r="D629" s="14" t="s">
-        <v>235</v>
+        <v>106</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E629" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -12328,11 +12336,11 @@
       <c r="C630" s="2">
         <v>107</v>
       </c>
-      <c r="D630" s="15" t="s">
-        <v>236</v>
+      <c r="D630" s="14" t="s">
+        <v>235</v>
       </c>
       <c r="E630" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -12346,10 +12354,10 @@
         <v>107</v>
       </c>
       <c r="D631" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E631" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -12362,11 +12370,11 @@
       <c r="C632" s="2">
         <v>107</v>
       </c>
-      <c r="D632" s="16" t="s">
-        <v>238</v>
+      <c r="D632" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="E632" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -12377,13 +12385,13 @@
         <v>-1</v>
       </c>
       <c r="C633" s="2">
-        <v>108</v>
-      </c>
-      <c r="D633" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="E633" s="1">
-        <v>1</v>
+        <v>107</v>
+      </c>
+      <c r="D633" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E633" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -12396,11 +12404,11 @@
       <c r="C634" s="2">
         <v>108</v>
       </c>
-      <c r="D634" s="15" t="s">
-        <v>236</v>
+      <c r="D634" s="14" t="s">
+        <v>235</v>
       </c>
       <c r="E634" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -12414,10 +12422,10 @@
         <v>108</v>
       </c>
       <c r="D635" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E635" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -12430,11 +12438,11 @@
       <c r="C636" s="2">
         <v>108</v>
       </c>
-      <c r="D636" s="16" t="s">
-        <v>238</v>
+      <c r="D636" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="E636" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -12445,13 +12453,13 @@
         <v>-1</v>
       </c>
       <c r="C637" s="2">
-        <v>109</v>
-      </c>
-      <c r="D637" s="17" t="s">
-        <v>230</v>
+        <v>108</v>
+      </c>
+      <c r="D637" s="16" t="s">
+        <v>238</v>
       </c>
       <c r="E637" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -12465,10 +12473,10 @@
         <v>109</v>
       </c>
       <c r="D638" s="17" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="E638" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -12482,10 +12490,10 @@
         <v>109</v>
       </c>
       <c r="D639" s="17" t="s">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="E639" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -12499,10 +12507,10 @@
         <v>109</v>
       </c>
       <c r="D640" s="17" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E640" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -12513,13 +12521,13 @@
         <v>-1</v>
       </c>
       <c r="C641" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D641" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E641" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -12533,10 +12541,10 @@
         <v>110</v>
       </c>
       <c r="D642" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E642" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643" spans="1:5">
@@ -12547,13 +12555,13 @@
         <v>-1</v>
       </c>
       <c r="C643" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D643" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E643" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -12567,10 +12575,10 @@
         <v>111</v>
       </c>
       <c r="D644" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E644" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -12584,10 +12592,10 @@
         <v>111</v>
       </c>
       <c r="D645" s="17" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="E645" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -12601,10 +12609,10 @@
         <v>111</v>
       </c>
       <c r="D646" s="17" t="s">
-        <v>244</v>
+        <v>163</v>
       </c>
       <c r="E646" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -12615,13 +12623,13 @@
         <v>-1</v>
       </c>
       <c r="C647" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D647" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E647" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -12635,10 +12643,10 @@
         <v>112</v>
       </c>
       <c r="D648" s="17" t="s">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="E648" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -12652,10 +12660,10 @@
         <v>112</v>
       </c>
       <c r="D649" s="17" t="s">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="E649" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -12669,10 +12677,10 @@
         <v>112</v>
       </c>
       <c r="D650" s="17" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="E650" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -12680,16 +12688,16 @@
         <v>650</v>
       </c>
       <c r="B651" s="2">
-        <v>646</v>
+        <v>-1</v>
       </c>
       <c r="C651" s="2">
-        <v>-1</v>
+        <v>112</v>
       </c>
       <c r="D651" s="17" t="s">
-        <v>246</v>
+        <v>105</v>
       </c>
       <c r="E651" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="652" spans="1:5">
@@ -12703,10 +12711,10 @@
         <v>-1</v>
       </c>
       <c r="D652" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E652" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -12720,10 +12728,10 @@
         <v>-1</v>
       </c>
       <c r="D653" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E653" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -12731,16 +12739,16 @@
         <v>653</v>
       </c>
       <c r="B654" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C654" s="2">
         <v>-1</v>
       </c>
       <c r="D654" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E654" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -12754,10 +12762,10 @@
         <v>-1</v>
       </c>
       <c r="D655" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E655" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="656" spans="1:5">
@@ -12771,10 +12779,10 @@
         <v>-1</v>
       </c>
       <c r="D656" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E656" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -12782,16 +12790,16 @@
         <v>656</v>
       </c>
       <c r="B657" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C657" s="2">
         <v>-1</v>
       </c>
       <c r="D657" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E657" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -12805,10 +12813,10 @@
         <v>-1</v>
       </c>
       <c r="D658" s="17" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E658" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -12822,10 +12830,10 @@
         <v>-1</v>
       </c>
       <c r="D659" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E659" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -12833,16 +12841,16 @@
         <v>659</v>
       </c>
       <c r="B660" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C660" s="2">
         <v>-1</v>
       </c>
       <c r="D660" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E660" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -12856,10 +12864,10 @@
         <v>-1</v>
       </c>
       <c r="D661" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E661" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -12873,10 +12881,10 @@
         <v>-1</v>
       </c>
       <c r="D662" s="17" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E662" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -12884,16 +12892,16 @@
         <v>662</v>
       </c>
       <c r="B663" s="2">
-        <v>-1</v>
+        <v>649</v>
       </c>
       <c r="C663" s="2">
-        <v>113</v>
+        <v>-1</v>
       </c>
       <c r="D663" s="17" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E663" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -12907,10 +12915,10 @@
         <v>113</v>
       </c>
       <c r="D664" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E664" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -12921,13 +12929,13 @@
         <v>-1</v>
       </c>
       <c r="C665" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D665" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E665" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -12941,10 +12949,10 @@
         <v>114</v>
       </c>
       <c r="D666" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E666" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -12958,10 +12966,10 @@
         <v>114</v>
       </c>
       <c r="D667" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E667" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -12972,13 +12980,13 @@
         <v>-1</v>
       </c>
       <c r="C668" s="2">
-        <v>115</v>
-      </c>
-      <c r="D668" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E668" s="2">
-        <v>1</v>
+        <v>114</v>
+      </c>
+      <c r="D668" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="E668" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -12992,10 +13000,10 @@
         <v>115</v>
       </c>
       <c r="D669" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E669" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -13009,10 +13017,10 @@
         <v>115</v>
       </c>
       <c r="D670" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E670" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -13025,11 +13033,11 @@
       <c r="C671" s="2">
         <v>115</v>
       </c>
-      <c r="D671" s="2" t="s">
-        <v>57</v>
+      <c r="D671" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="E671" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -13040,13 +13048,13 @@
         <v>-1</v>
       </c>
       <c r="C672" s="2">
-        <v>116</v>
-      </c>
-      <c r="D672" s="4" t="s">
-        <v>80</v>
+        <v>115</v>
+      </c>
+      <c r="D672" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E672" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -13060,10 +13068,10 @@
         <v>116</v>
       </c>
       <c r="D673" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E673" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="674" spans="1:5">
@@ -13076,11 +13084,11 @@
       <c r="C674" s="2">
         <v>116</v>
       </c>
-      <c r="D674" s="2" t="s">
-        <v>82</v>
+      <c r="D674" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="E674" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -13094,10 +13102,10 @@
         <v>116</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E675" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -13108,13 +13116,13 @@
         <v>-1</v>
       </c>
       <c r="C676" s="2">
-        <v>117</v>
-      </c>
-      <c r="D676" s="4" t="s">
-        <v>83</v>
+        <v>116</v>
+      </c>
+      <c r="D676" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E676" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="677" spans="1:5">
@@ -13128,10 +13136,10 @@
         <v>117</v>
       </c>
       <c r="D677" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E677" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -13144,11 +13152,11 @@
       <c r="C678" s="2">
         <v>117</v>
       </c>
-      <c r="D678" s="2" t="s">
-        <v>85</v>
+      <c r="D678" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="E678" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="679" spans="1:5">
@@ -13162,10 +13170,10 @@
         <v>117</v>
       </c>
       <c r="D679" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E679" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -13176,13 +13184,13 @@
         <v>-1</v>
       </c>
       <c r="C680" s="2">
-        <v>118</v>
-      </c>
-      <c r="D680" s="4" t="s">
-        <v>86</v>
+        <v>117</v>
+      </c>
+      <c r="D680" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E680" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -13196,10 +13204,10 @@
         <v>118</v>
       </c>
       <c r="D681" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E681" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -13212,11 +13220,11 @@
       <c r="C682" s="2">
         <v>118</v>
       </c>
-      <c r="D682" s="2" t="s">
-        <v>261</v>
+      <c r="D682" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="E682" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -13230,10 +13238,10 @@
         <v>118</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="E683" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -13247,10 +13255,10 @@
         <v>118</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="E684" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -13261,13 +13269,13 @@
         <v>-1</v>
       </c>
       <c r="C685" s="2">
-        <v>119</v>
-      </c>
-      <c r="D685" s="4" t="s">
-        <v>90</v>
+        <v>118</v>
+      </c>
+      <c r="D685" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E685" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -13281,10 +13289,10 @@
         <v>119</v>
       </c>
       <c r="D686" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E686" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -13297,11 +13305,11 @@
       <c r="C687" s="2">
         <v>119</v>
       </c>
-      <c r="D687" s="8" t="s">
-        <v>94</v>
+      <c r="D687" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="E687" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -13315,10 +13323,10 @@
         <v>119</v>
       </c>
       <c r="D688" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E688" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -13331,11 +13339,11 @@
       <c r="C689" s="2">
         <v>119</v>
       </c>
-      <c r="D689" s="2" t="s">
-        <v>96</v>
+      <c r="D689" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="E689" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="690" spans="1:5">
@@ -13346,13 +13354,13 @@
         <v>-1</v>
       </c>
       <c r="C690" s="2">
-        <v>120</v>
-      </c>
-      <c r="D690" s="4" t="s">
-        <v>97</v>
+        <v>119</v>
+      </c>
+      <c r="D690" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="E690" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -13366,10 +13374,10 @@
         <v>120</v>
       </c>
       <c r="D691" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E691" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="692" spans="1:5">
@@ -13380,13 +13388,13 @@
         <v>-1</v>
       </c>
       <c r="C692" s="2">
-        <v>121</v>
-      </c>
-      <c r="D692" s="4">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="D692" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="E692" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693" spans="1:5">
@@ -13400,10 +13408,10 @@
         <v>121</v>
       </c>
       <c r="D693" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E693" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -13417,10 +13425,10 @@
         <v>121</v>
       </c>
       <c r="D694" s="4">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E694" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -13434,10 +13442,10 @@
         <v>121</v>
       </c>
       <c r="D695" s="4">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E695" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="696" spans="1:5">
@@ -13451,10 +13459,10 @@
         <v>121</v>
       </c>
       <c r="D696" s="4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E696" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="697" spans="1:5">
@@ -13465,13 +13473,13 @@
         <v>-1</v>
       </c>
       <c r="C697" s="2">
-        <v>122</v>
-      </c>
-      <c r="D697" s="4" t="s">
-        <v>100</v>
+        <v>121</v>
+      </c>
+      <c r="D697" s="4">
+        <v>80</v>
       </c>
       <c r="E697" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="698" spans="1:5">
@@ -13485,10 +13493,10 @@
         <v>122</v>
       </c>
       <c r="D698" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E698" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="699" spans="1:5">
@@ -13501,11 +13509,11 @@
       <c r="C699" s="2">
         <v>122</v>
       </c>
-      <c r="D699" s="2" t="s">
-        <v>102</v>
+      <c r="D699" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E699" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -13516,13 +13524,13 @@
         <v>-1</v>
       </c>
       <c r="C700" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D700" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E700" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701" spans="1:5">
@@ -13536,10 +13544,10 @@
         <v>123</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E701" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702" spans="1:5">
@@ -13553,10 +13561,10 @@
         <v>123</v>
       </c>
       <c r="D702" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E702" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="703" spans="1:5">
@@ -13570,10 +13578,10 @@
         <v>123</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E703" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -13587,10 +13595,10 @@
         <v>123</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E704" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="705" spans="1:5">
@@ -13604,10 +13612,10 @@
         <v>123</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E705" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="706" spans="1:5">
@@ -13618,13 +13626,13 @@
         <v>-1</v>
       </c>
       <c r="C706" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E706" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="707" spans="1:5">
@@ -13638,10 +13646,10 @@
         <v>124</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E707" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708" spans="1:5">
@@ -13655,10 +13663,10 @@
         <v>124</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E708" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="709" spans="1:5">
@@ -13672,10 +13680,10 @@
         <v>124</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="E709" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="710" spans="1:5">
@@ -13689,10 +13697,10 @@
         <v>124</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="E710" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="711" spans="1:5">
@@ -13706,10 +13714,10 @@
         <v>124</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>263</v>
+        <v>113</v>
       </c>
       <c r="E711" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="712" spans="1:5">
@@ -13720,13 +13728,13 @@
         <v>-1</v>
       </c>
       <c r="C712" s="2">
-        <v>125</v>
-      </c>
-      <c r="D712" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="E712" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="713" spans="1:5">
@@ -13740,10 +13748,10 @@
         <v>125</v>
       </c>
       <c r="D713" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E713" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="714" spans="1:5">
@@ -13757,10 +13765,10 @@
         <v>125</v>
       </c>
       <c r="D714" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E714" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="715" spans="1:5">
@@ -13774,10 +13782,10 @@
         <v>125</v>
       </c>
       <c r="D715" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E715" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="716" spans="1:5">
@@ -13791,10 +13799,10 @@
         <v>125</v>
       </c>
       <c r="D716" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E716" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="717" spans="1:5">
@@ -13808,10 +13816,10 @@
         <v>125</v>
       </c>
       <c r="D717" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E717" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="718" spans="1:5">
@@ -13825,10 +13833,10 @@
         <v>125</v>
       </c>
       <c r="D718" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E718" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="719" spans="1:5">
@@ -13842,9 +13850,26 @@
         <v>125</v>
       </c>
       <c r="D719" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E719" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5">
+      <c r="A720" s="2">
+        <v>719</v>
+      </c>
+      <c r="B720" s="2">
+        <v>-1</v>
+      </c>
+      <c r="C720" s="2">
+        <v>125</v>
+      </c>
+      <c r="D720" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E719" s="2">
+      <c r="E720" s="2">
         <v>8</v>
       </c>
     </row>
